--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,122 +1563,6 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>119226061</v>
-      </c>
-      <c r="B9" t="n">
-        <v>105395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>490</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ljungsnärja</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Cuscuta epithymum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Hagen, Tryserum, Sm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>584976</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6445494</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Valdemarsvik</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Tryserum</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fläckvis på en sträcka av 20 m på V sidan vägen</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>103652</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584935.4076145188</v>
+        <v>584935</v>
       </c>
       <c r="R2" t="n">
-        <v>6445534.290752278</v>
+        <v>6445534</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>2003-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106039</v>
+        <v>106048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106048</v>
+        <v>106053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106053</v>
+        <v>106081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106081</v>
+        <v>106087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106087</v>
+        <v>106094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106094</v>
+        <v>106098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106098</v>
+        <v>106105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106108</v>
+        <v>106113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106113</v>
+        <v>106121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6578-2025 artfynd.xlsx
+++ b/artfynd/A 6578-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74137574</v>
       </c>
       <c r="B2" t="n">
-        <v>106121</v>
+        <v>106131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
